--- a/GameConfig/Scene/scene_config.xlsx
+++ b/GameConfig/Scene/scene_config.xlsx
@@ -214,6 +214,54 @@
       </c>
       <c t="inlineStr"/>
     </row>
+    <row r="5">
+      <c t="inlineStr">
+        <is>
+          <t>ColorfulTown</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>-20</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c t="inlineStr"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/GameConfig/Scene/scene_config.xlsx
+++ b/GameConfig/Scene/scene_config.xlsx
@@ -1,267 +1,1869 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="scene_config" sheetId="1" r:id="rId1"/>
+    <sheet name="scene_config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="22">
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="7"/>
+  <cols>
+    <col width="30.7142857142857" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.2857142857143" customWidth="1" style="1" min="10" max="10"/>
+    <col width="14.8571428571429" customWidth="1" style="1" min="11" max="11"/>
+    <col width="17.7142857142857" customWidth="1" style="1" min="12" max="12"/>
+    <col width="20.8571428571429" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27" customWidth="1" style="1" min="14" max="14"/>
+    <col width="18.8571428571429" customWidth="1" style="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>scene_id</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>spawn_x</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>spawn_z</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>is_default</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>grid_x</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>grid_z</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>origin_x</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>origin_z</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>zone_size</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>voxel_size_x</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>voxel_size_y</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>voxel_size_z</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>character_height</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>fill_interior_cavities</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>target_layers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>MainCity</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="L4" s="0" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c t="inlineStr">
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="O4" s="0" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c t="inlineStr"/>
     </row>
     <row r="5">
-      <c t="inlineStr">
-        <is>
-          <t>ColorfulTown</t>
-        </is>
-      </c>
-      <c t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>ColorfulTown_0_0</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>-65</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>-65</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>-130</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>-130</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>ColorfulTown_1_0</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>-130</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c t="inlineStr">
+      <c r="O6" s="0" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>ColorfulTown_0_1</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>-65</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>-130</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>ColorfulTown_1_1</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>